--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34458-2023 artfynd.xlsx
+++ b/artfynd/A 34458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344438</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
